--- a/data/trans_orig/LAWTONBRODY-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/LAWTONBRODY-Provincia-trans_orig.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,14; 7,62</t>
+          <t>6,17; 7,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,0; 7,37</t>
+          <t>5,94; 7,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,32; 7,16</t>
+          <t>5,32; 7,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,32; 7,59</t>
+          <t>6,21; 7,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,39; 5,88</t>
+          <t>4,29; 5,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,61; 6,4</t>
+          <t>4,68; 6,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,47; 7,44</t>
+          <t>6,6; 7,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,26; 6,46</t>
+          <t>5,29; 6,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,28; 6,48</t>
+          <t>5,23; 6,49</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,85; 7,59</t>
+          <t>6,79; 7,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,23; 6,97</t>
+          <t>5,37; 6,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,03; 7,67</t>
+          <t>7,09; 7,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,53; 7,42</t>
+          <t>6,49; 7,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,19; 6,5</t>
+          <t>5,28; 6,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,06; 7,04</t>
+          <t>6,01; 6,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,77; 7,38</t>
+          <t>6,8; 7,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,54; 6,58</t>
+          <t>5,57; 6,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,58; 7,24</t>
+          <t>6,58; 7,22</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,75; 7,68</t>
+          <t>6,7; 7,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,72; 7,18</t>
+          <t>5,65; 7,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,71; 7,56</t>
+          <t>6,63; 7,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,06; 7,0</t>
+          <t>5,99; 7,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,21; 6,72</t>
+          <t>5,1; 6,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,42; 7,6</t>
+          <t>6,48; 7,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,49; 7,2</t>
+          <t>6,44; 7,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,67; 6,72</t>
+          <t>5,67; 6,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,77; 7,49</t>
+          <t>6,75; 7,5</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,77; 7,61</t>
+          <t>6,68; 7,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,85; 7,13</t>
+          <t>5,93; 7,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,66; 7,49</t>
+          <t>6,62; 7,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,08; 7,07</t>
+          <t>6,08; 7,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,55; 6,64</t>
+          <t>5,58; 6,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,21; 7,24</t>
+          <t>6,15; 7,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,49; 7,18</t>
+          <t>6,53; 7,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,88; 6,74</t>
+          <t>5,9; 6,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,53; 7,28</t>
+          <t>6,53; 7,27</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,65; 6,97</t>
+          <t>4,73; 6,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,49; 7,38</t>
+          <t>5,32; 7,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,8; 7,79</t>
+          <t>6,84; 7,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,16; 6,94</t>
+          <t>5,17; 6,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,22; 6,66</t>
+          <t>5,19; 6,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,22; 6,77</t>
+          <t>5,22; 6,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,43; 6,75</t>
+          <t>5,38; 6,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,59; 6,81</t>
+          <t>5,61; 6,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,12; 7,16</t>
+          <t>6,16; 7,12</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,08; 7,16</t>
+          <t>6,02; 7,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,58; 6,96</t>
+          <t>5,52; 6,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,52; 7,0</t>
+          <t>5,67; 7,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,18; 7,27</t>
+          <t>6,24; 7,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,39; 6,84</t>
+          <t>5,45; 6,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,73; 7,04</t>
+          <t>5,63; 7,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,36; 7,13</t>
+          <t>6,35; 7,14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,66; 6,74</t>
+          <t>5,69; 6,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,92; 6,88</t>
+          <t>5,94; 6,89</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,98; 7,65</t>
+          <t>6,95; 7,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1347,37 +1347,37 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,53; 7,32</t>
+          <t>6,59; 7,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,46; 7,25</t>
+          <t>6,51; 7,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,91; 6,81</t>
+          <t>5,91; 6,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,64; 6,66</t>
+          <t>5,73; 6,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,91; 7,38</t>
+          <t>6,87; 7,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,26; 6,92</t>
+          <t>6,23; 6,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,23; 6,88</t>
+          <t>6,21; 6,85</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1447,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,54; 7,29</t>
+          <t>6,56; 7,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,89; 7,63</t>
+          <t>6,8; 7,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,02; 7,57</t>
+          <t>7,06; 7,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,22; 7,03</t>
+          <t>6,21; 7,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,32; 7,1</t>
+          <t>6,36; 7,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,63; 7,29</t>
+          <t>6,6; 7,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,49; 7,07</t>
+          <t>6,5; 7,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,7; 7,23</t>
+          <t>6,71; 7,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,94; 7,33</t>
+          <t>6,92; 7,35</t>
         </is>
       </c>
     </row>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,5; 6,96</t>
+          <t>6,5; 6,94</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,98; 7,28</t>
+          <t>6,99; 7,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,58; 6,93</t>
+          <t>6,58; 6,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,02; 6,43</t>
+          <t>6,01; 6,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1587,17 +1587,17 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,79; 7,02</t>
+          <t>6,78; 7,03</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,29; 6,59</t>
+          <t>6,3; 6,6</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,71; 6,96</t>
+          <t>6,7; 6,95</t>
         </is>
       </c>
     </row>
